--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -1,15 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasif\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB31655-791D-4F5B-8F7C-1CD85E7561F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Volunteers_table" sheetId="1" r:id="rId4"/>
+    <sheet name="Volunteers_table" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Volunteers_table!$J$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Volunteers_table!$J$1:$O$12</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eHgDEx91+4B+TguG9xbFx0OamAu6d15fKmxM7rxbXM4="/>
     </ext>
@@ -47,9 +68,6 @@
     <t>Kid</t>
   </si>
   <si>
-    <t>Overall</t>
-  </si>
-  <si>
     <t>Tournament</t>
   </si>
   <si>
@@ -93,40 +111,43 @@
   </si>
   <si>
     <t>Micah</t>
+  </si>
+  <si>
+    <t>Score</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
   <fonts count="5">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -136,7 +157,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -152,7 +173,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -166,55 +193,53 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf quotePrefix="1" borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -404,23 +429,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:O944"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="8" width="17.0"/>
-    <col customWidth="1" min="9" max="9" width="12.38"/>
-    <col customWidth="1" min="10" max="10" width="15.63"/>
+    <col min="1" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,480 +488,480 @@
         <v>7</v>
       </c>
       <c r="O1" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
+        <v>46256</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="6">
-        <v>46256.0</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="8" t="s">
+      <c r="K2" s="4">
+        <f>COUNTIF(E$2:E$964,$J2)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <f t="shared" ref="L2:N2" si="0">COUNTIF(F$2:F$964,$J2)</f>
+        <v>2</v>
+      </c>
+      <c r="M2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <f>K2*2+SUM(L2:N2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6">
+        <v>46256</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="F3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="4">
-        <f t="shared" ref="K2:K11" si="2">COUNTIF(E$2:E$964,$J2)*2</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <f t="shared" ref="L2:N2" si="1">COUNTIF(F$2:F$964,$J2)</f>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:K11" si="1">COUNTIF(E$2:E$964,$J3)</f>
         <v>1</v>
       </c>
-      <c r="M2" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N2" s="4">
+      <c r="L3" s="4">
+        <f t="shared" ref="L3:N3" si="2">COUNTIF(F$2:F$964,$J3)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O3" s="4">
+        <f t="shared" ref="O3:O11" si="3">K3*2+SUM(L3:N3)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A4" s="5">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6">
+        <v>46256</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="O2" s="4">
-        <f t="shared" ref="O2:O11" si="4">SUM(K2:N2)</f>
+      <c r="L4" s="4">
+        <f t="shared" ref="L4:N4" si="4">COUNTIF(F$2:F$964,$J4)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6">
+        <v>46263</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L5" s="4">
+        <f t="shared" ref="L5:N5" si="5">COUNTIF(F$2:F$964,$J5)</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A6" s="5">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46270</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L6" s="4">
+        <f t="shared" ref="L6:N6" si="6">COUNTIF(F$2:F$964,$J6)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="N6" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A7" s="5">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6">
+        <v>46277</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L7" s="4">
+        <f t="shared" ref="L7:N7" si="7">COUNTIF(F$2:F$964,$J7)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="6">
-        <v>46256.0</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="N7" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46284</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="E8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="4">
+        <f t="shared" ref="L8:N8" si="8">COUNTIF(F$2:F$964,$J8)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A9" s="5">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46291</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="10" t="s">
+      <c r="G9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="4">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L3" s="4">
-        <f t="shared" ref="L3:N3" si="3">COUNTIF(F$2:F$964,$J3)</f>
+      <c r="H9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <f t="shared" ref="L9:N9" si="9">COUNTIF(F$2:F$964,$J9)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N9" s="4">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A10" s="5">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46298</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <f t="shared" ref="L10:N10" si="10">COUNTIF(F$2:F$964,$J10)</f>
         <v>1</v>
       </c>
-      <c r="M3" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="11">
-        <v>2.0</v>
-      </c>
-      <c r="B4" s="6">
-        <v>46256.0</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="4">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L4" s="4">
-        <f t="shared" ref="L4:N4" si="5">COUNTIF(F$2:F$964,$J4)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="N4" s="4">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="11">
-        <v>3.0</v>
-      </c>
-      <c r="B5" s="6">
-        <v>46263.0</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" s="4">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L5" s="4">
-        <f t="shared" ref="L5:N5" si="6">COUNTIF(F$2:F$964,$J5)</f>
-        <v>1</v>
-      </c>
-      <c r="M5" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="11">
-        <v>4.0</v>
-      </c>
-      <c r="B6" s="6">
-        <v>46270.0</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="4">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L6" s="4">
-        <f t="shared" ref="L6:N6" si="7">COUNTIF(F$2:F$964,$J6)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="N6" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O6" s="4">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="11">
-        <v>5.0</v>
-      </c>
-      <c r="B7" s="6">
-        <v>46277.0</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="4">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L7" s="4">
-        <f t="shared" ref="L7:N7" si="8">COUNTIF(F$2:F$964,$J7)</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="N7" s="4">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O7" s="4">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="11">
-        <v>6.0</v>
-      </c>
-      <c r="B8" s="6">
-        <v>46284.0</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="4">
-        <f t="shared" ref="L8:N8" si="9">COUNTIF(F$2:F$964,$J8)</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="4">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="11">
-        <v>7.0</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46291.0</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L9" s="4">
-        <f t="shared" ref="L9:N9" si="10">COUNTIF(F$2:F$964,$J9)</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="4">
+      <c r="M10" s="4">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="N9" s="4">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="O9" s="4">
-        <f t="shared" si="4"/>
+      <c r="O10" s="4">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="J11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="4">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="11">
-        <v>8.0</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46298.0</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L10" s="4">
-        <f t="shared" ref="L10:N10" si="11">COUNTIF(F$2:F$964,$J10)</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="4">
+      <c r="L11" s="4">
+        <f t="shared" ref="L11:N11" si="11">COUNTIF(F$2:F$964,$J11)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N11" s="4">
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="O10" s="4">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="J11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="4">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L11" s="4">
-        <f t="shared" ref="L11:N11" si="12">COUNTIF(F$2:F$964,$J11)</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <f t="shared" si="12"/>
-        <v>1</v>
-      </c>
       <c r="O11" s="4">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -951,522 +978,522 @@
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="14"/>
-      <c r="B44" s="14"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="14"/>
-      <c r="B45" s="14"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="14"/>
-      <c r="B46" s="14"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="14"/>
-      <c r="B49" s="14"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="14"/>
-      <c r="B50" s="14"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="14"/>
-      <c r="B51" s="14"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="14"/>
-      <c r="B52" s="14"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="14"/>
-      <c r="B53" s="14"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="14"/>
-      <c r="B54" s="14"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="14"/>
-      <c r="B55" s="14"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="14"/>
-      <c r="B56" s="14"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="14"/>
-      <c r="B57" s="14"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="14"/>
-      <c r="B58" s="14"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="14"/>
-      <c r="B59" s="14"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="14"/>
-      <c r="B60" s="14"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="14"/>
-      <c r="B61" s="14"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="14"/>
-      <c r="B62" s="14"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="14"/>
-      <c r="B63" s="14"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="14"/>
-      <c r="B64" s="14"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="14"/>
-      <c r="B65" s="14"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="14"/>
-      <c r="B66" s="14"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="14"/>
-      <c r="B67" s="14"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="14"/>
-      <c r="B68" s="14"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="14"/>
-      <c r="B69" s="14"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="14"/>
-      <c r="B70" s="14"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="14"/>
-      <c r="B71" s="14"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="14"/>
-      <c r="B72" s="14"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="14"/>
-      <c r="B73" s="14"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="14"/>
-      <c r="B74" s="14"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="14"/>
-      <c r="B75" s="14"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="14"/>
-      <c r="B76" s="14"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="14"/>
-      <c r="B77" s="14"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="14"/>
-      <c r="B78" s="14"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="14"/>
-      <c r="B79" s="14"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="14"/>
-      <c r="B80" s="14"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="14"/>
-      <c r="B81" s="14"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="14"/>
-      <c r="B82" s="14"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="14"/>
-      <c r="B83" s="14"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="14"/>
-      <c r="B84" s="14"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="14"/>
-      <c r="B85" s="14"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="14"/>
-      <c r="B86" s="14"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="14"/>
-      <c r="B87" s="14"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="14"/>
-      <c r="B88" s="14"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="14"/>
-      <c r="B89" s="14"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="14"/>
-      <c r="B90" s="14"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="14"/>
-      <c r="B91" s="14"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="14"/>
-      <c r="B92" s="14"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="14"/>
-      <c r="B93" s="14"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="14"/>
-      <c r="B94" s="14"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="14"/>
-      <c r="B95" s="14"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="14"/>
-      <c r="B96" s="14"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="14"/>
-      <c r="B97" s="14"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="14"/>
-      <c r="B98" s="14"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="14"/>
-      <c r="B99" s="14"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="14"/>
-      <c r="B100" s="14"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="14"/>
-      <c r="B101" s="14"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="14"/>
-      <c r="B102" s="14"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="14"/>
-      <c r="B103" s="14"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="14"/>
-      <c r="B104" s="14"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="14"/>
-      <c r="B105" s="14"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="14"/>
-      <c r="B106" s="14"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="14"/>
-      <c r="B107" s="14"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="14"/>
-      <c r="B108" s="14"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="14"/>
-      <c r="B109" s="14"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="14"/>
-      <c r="B110" s="14"/>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="14"/>
-      <c r="B111" s="14"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="14"/>
-      <c r="B112" s="14"/>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="14"/>
-      <c r="B113" s="14"/>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="14"/>
-      <c r="B114" s="14"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="14"/>
-      <c r="B115" s="14"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="14"/>
-      <c r="B116" s="14"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="14"/>
-      <c r="B117" s="14"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="14"/>
-      <c r="B118" s="14"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="14"/>
-      <c r="B119" s="14"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="14"/>
-      <c r="B120" s="14"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="14"/>
-      <c r="B121" s="14"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="14"/>
-      <c r="B122" s="14"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="14"/>
-      <c r="B123" s="14"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="14"/>
-      <c r="B124" s="14"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="14"/>
-      <c r="B125" s="14"/>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="14"/>
-      <c r="B126" s="14"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="14"/>
-      <c r="B127" s="14"/>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="14"/>
-      <c r="B128" s="14"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="14"/>
-      <c r="B129" s="14"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="14"/>
-      <c r="B130" s="14"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="14"/>
-      <c r="B131" s="14"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="14"/>
-      <c r="B132" s="14"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="14"/>
-      <c r="B133" s="14"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="14"/>
-      <c r="B134" s="14"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="14"/>
-      <c r="B135" s="14"/>
-    </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="14"/>
-      <c r="B136" s="14"/>
-    </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="14"/>
-      <c r="B137" s="14"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="14"/>
-      <c r="B138" s="14"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="14"/>
-      <c r="B139" s="14"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="14"/>
-      <c r="B140" s="14"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="14"/>
-      <c r="B141" s="14"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="14"/>
-      <c r="B142" s="14"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="14"/>
-      <c r="B143" s="14"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="14"/>
-      <c r="B144" s="14"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="14"/>
-      <c r="B145" s="14"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="14"/>
-      <c r="B146" s="14"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="14"/>
-      <c r="B147" s="14"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="14"/>
-      <c r="B148" s="14"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="14"/>
-      <c r="B149" s="14"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="14"/>
-      <c r="B150" s="14"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="14"/>
-      <c r="B151" s="14"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="14"/>
-      <c r="B152" s="14"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="14"/>
-      <c r="B153" s="14"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="14"/>
-      <c r="B154" s="14"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="14"/>
-      <c r="B155" s="14"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="14"/>
-      <c r="B156" s="14"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="14"/>
-      <c r="B157" s="14"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="14"/>
-      <c r="B158" s="14"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="14"/>
-      <c r="B159" s="14"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="14"/>
-      <c r="B160" s="14"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="14"/>
-      <c r="B161" s="14"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="14"/>
-      <c r="B162" s="14"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="14"/>
-      <c r="B163" s="14"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="14"/>
-      <c r="B164" s="14"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="14"/>
-      <c r="B165" s="14"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="14"/>
-      <c r="B166" s="14"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="33" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A43" s="12"/>
+      <c r="B43" s="12"/>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A44" s="12"/>
+      <c r="B44" s="12"/>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A45" s="12"/>
+      <c r="B45" s="12"/>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A46" s="12"/>
+      <c r="B46" s="12"/>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A47" s="12"/>
+      <c r="B47" s="12"/>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A48" s="12"/>
+      <c r="B48" s="12"/>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A50" s="12"/>
+      <c r="B50" s="12"/>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A54" s="12"/>
+      <c r="B54" s="12"/>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+    </row>
+    <row r="59" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+    </row>
+    <row r="60" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+    </row>
+    <row r="62" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+    </row>
+    <row r="63" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+    </row>
+    <row r="66" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+    </row>
+    <row r="69" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A69" s="12"/>
+      <c r="B69" s="12"/>
+    </row>
+    <row r="70" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
+    </row>
+    <row r="72" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A72" s="12"/>
+      <c r="B72" s="12"/>
+    </row>
+    <row r="73" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A73" s="12"/>
+      <c r="B73" s="12"/>
+    </row>
+    <row r="74" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
+    </row>
+    <row r="75" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
+    </row>
+    <row r="76" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A76" s="12"/>
+      <c r="B76" s="12"/>
+    </row>
+    <row r="77" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A77" s="12"/>
+      <c r="B77" s="12"/>
+    </row>
+    <row r="78" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A78" s="12"/>
+      <c r="B78" s="12"/>
+    </row>
+    <row r="79" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
+    </row>
+    <row r="80" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A80" s="12"/>
+      <c r="B80" s="12"/>
+    </row>
+    <row r="81" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A81" s="12"/>
+      <c r="B81" s="12"/>
+    </row>
+    <row r="82" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A82" s="12"/>
+      <c r="B82" s="12"/>
+    </row>
+    <row r="83" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A83" s="12"/>
+      <c r="B83" s="12"/>
+    </row>
+    <row r="84" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A84" s="12"/>
+      <c r="B84" s="12"/>
+    </row>
+    <row r="85" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A85" s="12"/>
+      <c r="B85" s="12"/>
+    </row>
+    <row r="86" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A86" s="12"/>
+      <c r="B86" s="12"/>
+    </row>
+    <row r="87" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A87" s="12"/>
+      <c r="B87" s="12"/>
+    </row>
+    <row r="88" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A88" s="12"/>
+      <c r="B88" s="12"/>
+    </row>
+    <row r="89" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A89" s="12"/>
+      <c r="B89" s="12"/>
+    </row>
+    <row r="90" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A90" s="12"/>
+      <c r="B90" s="12"/>
+    </row>
+    <row r="91" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A91" s="12"/>
+      <c r="B91" s="12"/>
+    </row>
+    <row r="92" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A92" s="12"/>
+      <c r="B92" s="12"/>
+    </row>
+    <row r="93" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A93" s="12"/>
+      <c r="B93" s="12"/>
+    </row>
+    <row r="94" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A94" s="12"/>
+      <c r="B94" s="12"/>
+    </row>
+    <row r="95" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A95" s="12"/>
+      <c r="B95" s="12"/>
+    </row>
+    <row r="96" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A96" s="12"/>
+      <c r="B96" s="12"/>
+    </row>
+    <row r="97" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A97" s="12"/>
+      <c r="B97" s="12"/>
+    </row>
+    <row r="98" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A98" s="12"/>
+      <c r="B98" s="12"/>
+    </row>
+    <row r="99" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A99" s="12"/>
+      <c r="B99" s="12"/>
+    </row>
+    <row r="100" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A100" s="12"/>
+      <c r="B100" s="12"/>
+    </row>
+    <row r="101" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A101" s="12"/>
+      <c r="B101" s="12"/>
+    </row>
+    <row r="102" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A102" s="12"/>
+      <c r="B102" s="12"/>
+    </row>
+    <row r="103" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A103" s="12"/>
+      <c r="B103" s="12"/>
+    </row>
+    <row r="104" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A104" s="12"/>
+      <c r="B104" s="12"/>
+    </row>
+    <row r="105" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A105" s="12"/>
+      <c r="B105" s="12"/>
+    </row>
+    <row r="106" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A106" s="12"/>
+      <c r="B106" s="12"/>
+    </row>
+    <row r="107" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A107" s="12"/>
+      <c r="B107" s="12"/>
+    </row>
+    <row r="108" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A108" s="12"/>
+      <c r="B108" s="12"/>
+    </row>
+    <row r="109" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A109" s="12"/>
+      <c r="B109" s="12"/>
+    </row>
+    <row r="110" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A110" s="12"/>
+      <c r="B110" s="12"/>
+    </row>
+    <row r="111" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A111" s="12"/>
+      <c r="B111" s="12"/>
+    </row>
+    <row r="112" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A112" s="12"/>
+      <c r="B112" s="12"/>
+    </row>
+    <row r="113" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A113" s="12"/>
+      <c r="B113" s="12"/>
+    </row>
+    <row r="114" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A114" s="12"/>
+      <c r="B114" s="12"/>
+    </row>
+    <row r="115" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A115" s="12"/>
+      <c r="B115" s="12"/>
+    </row>
+    <row r="116" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A116" s="12"/>
+      <c r="B116" s="12"/>
+    </row>
+    <row r="117" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A117" s="12"/>
+      <c r="B117" s="12"/>
+    </row>
+    <row r="118" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A118" s="12"/>
+      <c r="B118" s="12"/>
+    </row>
+    <row r="119" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A119" s="12"/>
+      <c r="B119" s="12"/>
+    </row>
+    <row r="120" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A120" s="12"/>
+      <c r="B120" s="12"/>
+    </row>
+    <row r="121" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A121" s="12"/>
+      <c r="B121" s="12"/>
+    </row>
+    <row r="122" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A122" s="12"/>
+      <c r="B122" s="12"/>
+    </row>
+    <row r="123" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A123" s="12"/>
+      <c r="B123" s="12"/>
+    </row>
+    <row r="124" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A124" s="12"/>
+      <c r="B124" s="12"/>
+    </row>
+    <row r="125" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A125" s="12"/>
+      <c r="B125" s="12"/>
+    </row>
+    <row r="126" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A126" s="12"/>
+      <c r="B126" s="12"/>
+    </row>
+    <row r="127" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A127" s="12"/>
+      <c r="B127" s="12"/>
+    </row>
+    <row r="128" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A128" s="12"/>
+      <c r="B128" s="12"/>
+    </row>
+    <row r="129" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A129" s="12"/>
+      <c r="B129" s="12"/>
+    </row>
+    <row r="130" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A130" s="12"/>
+      <c r="B130" s="12"/>
+    </row>
+    <row r="131" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A131" s="12"/>
+      <c r="B131" s="12"/>
+    </row>
+    <row r="132" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A132" s="12"/>
+      <c r="B132" s="12"/>
+    </row>
+    <row r="133" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A133" s="12"/>
+      <c r="B133" s="12"/>
+    </row>
+    <row r="134" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A134" s="12"/>
+      <c r="B134" s="12"/>
+    </row>
+    <row r="135" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A135" s="12"/>
+      <c r="B135" s="12"/>
+    </row>
+    <row r="136" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A136" s="12"/>
+      <c r="B136" s="12"/>
+    </row>
+    <row r="137" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A137" s="12"/>
+      <c r="B137" s="12"/>
+    </row>
+    <row r="138" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A138" s="12"/>
+      <c r="B138" s="12"/>
+    </row>
+    <row r="139" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A139" s="12"/>
+      <c r="B139" s="12"/>
+    </row>
+    <row r="140" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A140" s="12"/>
+      <c r="B140" s="12"/>
+    </row>
+    <row r="141" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A141" s="12"/>
+      <c r="B141" s="12"/>
+    </row>
+    <row r="142" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A142" s="12"/>
+      <c r="B142" s="12"/>
+    </row>
+    <row r="143" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A143" s="12"/>
+      <c r="B143" s="12"/>
+    </row>
+    <row r="144" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A144" s="12"/>
+      <c r="B144" s="12"/>
+    </row>
+    <row r="145" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A145" s="12"/>
+      <c r="B145" s="12"/>
+    </row>
+    <row r="146" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A146" s="12"/>
+      <c r="B146" s="12"/>
+    </row>
+    <row r="147" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A147" s="12"/>
+      <c r="B147" s="12"/>
+    </row>
+    <row r="148" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A148" s="12"/>
+      <c r="B148" s="12"/>
+    </row>
+    <row r="149" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A149" s="12"/>
+      <c r="B149" s="12"/>
+    </row>
+    <row r="150" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A150" s="12"/>
+      <c r="B150" s="12"/>
+    </row>
+    <row r="151" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A151" s="12"/>
+      <c r="B151" s="12"/>
+    </row>
+    <row r="152" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A152" s="12"/>
+      <c r="B152" s="12"/>
+    </row>
+    <row r="153" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A153" s="12"/>
+      <c r="B153" s="12"/>
+    </row>
+    <row r="154" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A154" s="12"/>
+      <c r="B154" s="12"/>
+    </row>
+    <row r="155" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A155" s="12"/>
+      <c r="B155" s="12"/>
+    </row>
+    <row r="156" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A156" s="12"/>
+      <c r="B156" s="12"/>
+    </row>
+    <row r="157" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A157" s="12"/>
+      <c r="B157" s="12"/>
+    </row>
+    <row r="158" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A158" s="12"/>
+      <c r="B158" s="12"/>
+    </row>
+    <row r="159" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A159" s="12"/>
+      <c r="B159" s="12"/>
+    </row>
+    <row r="160" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A160" s="12"/>
+      <c r="B160" s="12"/>
+    </row>
+    <row r="161" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A161" s="12"/>
+      <c r="B161" s="12"/>
+    </row>
+    <row r="162" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A162" s="12"/>
+      <c r="B162" s="12"/>
+    </row>
+    <row r="163" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A163" s="12"/>
+      <c r="B163" s="12"/>
+    </row>
+    <row r="164" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A164" s="12"/>
+      <c r="B164" s="12"/>
+    </row>
+    <row r="165" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A165" s="12"/>
+      <c r="B165" s="12"/>
+    </row>
+    <row r="166" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A166" s="12"/>
+      <c r="B166" s="12"/>
+    </row>
+    <row r="167" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="168" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="169" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="170" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="171" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="172" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="173" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="174" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="175" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="176" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="177" ht="15.75" customHeight="1"/>
     <row r="178" ht="15.75" customHeight="1"/>
     <row r="179" ht="15.75" customHeight="1"/>
@@ -2236,10 +2263,14 @@
     <row r="943" ht="15.75" customHeight="1"/>
     <row r="944" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$J$1:$O$12"/>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <autoFilter ref="J1:O12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{08f6f869-1ed0-46b3-a227-1d3e52347e28}" enabled="1" method="Standard" siteId="{98e9ba89-e1a1-4e38-9007-8bdabc25de1d}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -1,38 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasif\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB31655-791D-4F5B-8F7C-1CD85E7561F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Volunteers_table" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Volunteers_table" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Volunteers_table!$J$1:$O$12</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Volunteers_table!$J$1:$O$12</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="eHgDEx91+4B+TguG9xbFx0OamAu6d15fKmxM7rxbXM4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="C6zCwR/TZey+cf8qVItD04OlODhU8xubcFG/MqVZmog="/>
     </ext>
   </extLst>
 </workbook>
@@ -68,6 +47,9 @@
     <t>Kid</t>
   </si>
   <si>
+    <t>Score</t>
+  </si>
+  <si>
     <t>Tournament</t>
   </si>
   <si>
@@ -107,47 +89,44 @@
     <t>Hugo</t>
   </si>
   <si>
+    <t>Micah</t>
+  </si>
+  <si>
     <t>Mulu</t>
-  </si>
-  <si>
-    <t>Micah</t>
-  </si>
-  <si>
-    <t>Score</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
   <fonts count="5">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF1F1F1F"/>
       <name val="Google Sans"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -157,7 +136,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -173,13 +152,7 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -193,53 +166,52 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="14">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf quotePrefix="1" borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -429,25 +401,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O944"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" customWidth="1"/>
+    <col customWidth="1" min="1" max="8" width="17.0"/>
+    <col customWidth="1" min="9" max="9" width="12.38"/>
+    <col customWidth="1" min="10" max="10" width="15.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,92 +458,92 @@
         <v>7</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="6">
+        <v>46256.0</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="4">
+        <f t="shared" ref="K2:N2" si="1">COUNTIF(E$2:E$964,$J2)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="M2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <f t="shared" ref="O2:O11" si="3">K2*2+SUM(L2:N2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="6">
+        <v>46256.0</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:N3" si="2">COUNTIF(E$2:E$964,$J3)</f>
         <v>1</v>
       </c>
-      <c r="B2" s="6">
-        <v>46256</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="4">
-        <f>COUNTIF(E$2:E$964,$J2)</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <f t="shared" ref="L2:N2" si="0">COUNTIF(F$2:F$964,$J2)</f>
-        <v>2</v>
-      </c>
-      <c r="M2" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N2" s="4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
-        <f>K2*2+SUM(L2:N2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6">
-        <v>46256</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K3" s="4">
-        <f t="shared" ref="K3:K11" si="1">COUNTIF(E$2:E$964,$J3)</f>
-        <v>1</v>
-      </c>
       <c r="L3" s="4">
-        <f t="shared" ref="L3:N3" si="2">COUNTIF(F$2:F$964,$J3)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M3" s="4">
@@ -585,44 +555,44 @@
         <v>1</v>
       </c>
       <c r="O3" s="4">
-        <f t="shared" ref="O3:O11" si="3">K3*2+SUM(L3:N3)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="5">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="B4" s="6">
-        <v>46256</v>
+        <v>46256.0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K4:N4" si="4">COUNTIF(E$2:E$964,$J4)</f>
         <v>1</v>
       </c>
       <c r="L4" s="4">
-        <f t="shared" ref="L4:N4" si="4">COUNTIF(F$2:F$964,$J4)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="M4" s="4">
@@ -638,40 +608,40 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="5">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="B5" s="6">
-        <v>46263</v>
+        <v>46263.0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="J5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K5:N5" si="5">COUNTIF(E$2:E$964,$J5)</f>
         <v>1</v>
       </c>
       <c r="L5" s="4">
-        <f t="shared" ref="L5:N5" si="5">COUNTIF(F$2:F$964,$J5)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="M5" s="4">
@@ -687,45 +657,45 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="5">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="B6" s="6">
-        <v>46270</v>
+        <v>46270.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K6" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K6:N6" si="6">COUNTIF(E$2:E$964,$J6)</f>
         <v>1</v>
       </c>
       <c r="L6" s="4">
-        <f t="shared" ref="L6:N6" si="6">COUNTIF(F$2:F$964,$J6)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4">
         <f t="shared" si="6"/>
@@ -733,43 +703,43 @@
       </c>
       <c r="O6" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="5">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="B7" s="6">
-        <v>46277</v>
+        <v>46277.0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>17</v>
-      </c>
       <c r="H7" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K7:N7" si="7">COUNTIF(E$2:E$964,$J7)</f>
         <v>1</v>
       </c>
       <c r="L7" s="4">
-        <f t="shared" ref="L7:N7" si="7">COUNTIF(F$2:F$964,$J7)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="M7" s="4">
@@ -785,40 +755,40 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="5">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="B8" s="6">
-        <v>46284</v>
+        <v>46284.0</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K8:N8" si="8">COUNTIF(E$2:E$964,$J8)</f>
         <v>0</v>
       </c>
       <c r="L8" s="4">
-        <f t="shared" ref="L8:N8" si="8">COUNTIF(F$2:F$964,$J8)</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M8" s="4">
@@ -834,45 +804,45 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="5">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="B9" s="6">
-        <v>46291</v>
+        <v>46291.0</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="J9" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K9" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K9:N9" si="9">COUNTIF(E$2:E$964,$J9)</f>
         <v>0</v>
       </c>
       <c r="L9" s="4">
-        <f t="shared" ref="L9:N9" si="9">COUNTIF(F$2:F$964,$J9)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="M9" s="4">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="4">
         <f t="shared" si="9"/>
@@ -880,43 +850,43 @@
       </c>
       <c r="O9" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="5">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="B10" s="6">
-        <v>46298</v>
+        <v>46298.0</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="8" t="s">
         <v>21</v>
       </c>
+      <c r="G10" s="12" t="s">
+        <v>24</v>
+      </c>
       <c r="H10" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K10:N10" si="10">COUNTIF(E$2:E$964,$J10)</f>
         <v>0</v>
       </c>
       <c r="L10" s="4">
-        <f t="shared" ref="L10:N10" si="10">COUNTIF(F$2:F$964,$J10)</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="M10" s="4">
@@ -932,16 +902,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="J11" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K11" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="K11:N11" si="11">COUNTIF(E$2:E$964,$J11)</f>
         <v>1</v>
       </c>
       <c r="L11" s="4">
-        <f t="shared" ref="L11:N11" si="11">COUNTIF(F$2:F$964,$J11)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="M11" s="4">
@@ -957,11 +927,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1"/>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -978,522 +948,522 @@
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
-    </row>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
-    </row>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
-    </row>
-    <row r="46" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
-    </row>
-    <row r="47" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
-    </row>
-    <row r="48" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
-    </row>
-    <row r="49" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
-    </row>
-    <row r="51" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
-    </row>
-    <row r="52" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
-    </row>
-    <row r="53" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
-    </row>
-    <row r="54" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
-    </row>
-    <row r="55" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
-    </row>
-    <row r="56" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
-    </row>
-    <row r="57" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
-    </row>
-    <row r="58" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
-    </row>
-    <row r="59" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-    </row>
-    <row r="60" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
-    </row>
-    <row r="61" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
-    </row>
-    <row r="62" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
-    </row>
-    <row r="63" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
-    </row>
-    <row r="64" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
-    </row>
-    <row r="65" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
-    </row>
-    <row r="66" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
-    </row>
-    <row r="67" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12"/>
-    </row>
-    <row r="68" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A68" s="12"/>
-      <c r="B68" s="12"/>
-    </row>
-    <row r="69" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A69" s="12"/>
-      <c r="B69" s="12"/>
-    </row>
-    <row r="70" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
-    </row>
-    <row r="71" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A71" s="12"/>
-      <c r="B71" s="12"/>
-    </row>
-    <row r="72" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A72" s="12"/>
-      <c r="B72" s="12"/>
-    </row>
-    <row r="73" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A73" s="12"/>
-      <c r="B73" s="12"/>
-    </row>
-    <row r="74" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A74" s="12"/>
-      <c r="B74" s="12"/>
-    </row>
-    <row r="75" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A75" s="12"/>
-      <c r="B75" s="12"/>
-    </row>
-    <row r="76" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A76" s="12"/>
-      <c r="B76" s="12"/>
-    </row>
-    <row r="77" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A77" s="12"/>
-      <c r="B77" s="12"/>
-    </row>
-    <row r="78" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
-    </row>
-    <row r="79" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A79" s="12"/>
-      <c r="B79" s="12"/>
-    </row>
-    <row r="80" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A80" s="12"/>
-      <c r="B80" s="12"/>
-    </row>
-    <row r="81" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A81" s="12"/>
-      <c r="B81" s="12"/>
-    </row>
-    <row r="82" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A82" s="12"/>
-      <c r="B82" s="12"/>
-    </row>
-    <row r="83" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A83" s="12"/>
-      <c r="B83" s="12"/>
-    </row>
-    <row r="84" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A84" s="12"/>
-      <c r="B84" s="12"/>
-    </row>
-    <row r="85" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A85" s="12"/>
-      <c r="B85" s="12"/>
-    </row>
-    <row r="86" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A86" s="12"/>
-      <c r="B86" s="12"/>
-    </row>
-    <row r="87" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A87" s="12"/>
-      <c r="B87" s="12"/>
-    </row>
-    <row r="88" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A88" s="12"/>
-      <c r="B88" s="12"/>
-    </row>
-    <row r="89" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A89" s="12"/>
-      <c r="B89" s="12"/>
-    </row>
-    <row r="90" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A90" s="12"/>
-      <c r="B90" s="12"/>
-    </row>
-    <row r="91" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A91" s="12"/>
-      <c r="B91" s="12"/>
-    </row>
-    <row r="92" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A92" s="12"/>
-      <c r="B92" s="12"/>
-    </row>
-    <row r="93" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A93" s="12"/>
-      <c r="B93" s="12"/>
-    </row>
-    <row r="94" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A94" s="12"/>
-      <c r="B94" s="12"/>
-    </row>
-    <row r="95" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A95" s="12"/>
-      <c r="B95" s="12"/>
-    </row>
-    <row r="96" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A96" s="12"/>
-      <c r="B96" s="12"/>
-    </row>
-    <row r="97" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A97" s="12"/>
-      <c r="B97" s="12"/>
-    </row>
-    <row r="98" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A98" s="12"/>
-      <c r="B98" s="12"/>
-    </row>
-    <row r="99" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A99" s="12"/>
-      <c r="B99" s="12"/>
-    </row>
-    <row r="100" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A100" s="12"/>
-      <c r="B100" s="12"/>
-    </row>
-    <row r="101" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A101" s="12"/>
-      <c r="B101" s="12"/>
-    </row>
-    <row r="102" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A102" s="12"/>
-      <c r="B102" s="12"/>
-    </row>
-    <row r="103" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A103" s="12"/>
-      <c r="B103" s="12"/>
-    </row>
-    <row r="104" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A104" s="12"/>
-      <c r="B104" s="12"/>
-    </row>
-    <row r="105" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A105" s="12"/>
-      <c r="B105" s="12"/>
-    </row>
-    <row r="106" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A106" s="12"/>
-      <c r="B106" s="12"/>
-    </row>
-    <row r="107" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A107" s="12"/>
-      <c r="B107" s="12"/>
-    </row>
-    <row r="108" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A108" s="12"/>
-      <c r="B108" s="12"/>
-    </row>
-    <row r="109" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A109" s="12"/>
-      <c r="B109" s="12"/>
-    </row>
-    <row r="110" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A110" s="12"/>
-      <c r="B110" s="12"/>
-    </row>
-    <row r="111" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A111" s="12"/>
-      <c r="B111" s="12"/>
-    </row>
-    <row r="112" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A112" s="12"/>
-      <c r="B112" s="12"/>
-    </row>
-    <row r="113" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A113" s="12"/>
-      <c r="B113" s="12"/>
-    </row>
-    <row r="114" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A114" s="12"/>
-      <c r="B114" s="12"/>
-    </row>
-    <row r="115" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A115" s="12"/>
-      <c r="B115" s="12"/>
-    </row>
-    <row r="116" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A116" s="12"/>
-      <c r="B116" s="12"/>
-    </row>
-    <row r="117" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A117" s="12"/>
-      <c r="B117" s="12"/>
-    </row>
-    <row r="118" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A118" s="12"/>
-      <c r="B118" s="12"/>
-    </row>
-    <row r="119" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A119" s="12"/>
-      <c r="B119" s="12"/>
-    </row>
-    <row r="120" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A120" s="12"/>
-      <c r="B120" s="12"/>
-    </row>
-    <row r="121" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A121" s="12"/>
-      <c r="B121" s="12"/>
-    </row>
-    <row r="122" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A122" s="12"/>
-      <c r="B122" s="12"/>
-    </row>
-    <row r="123" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A123" s="12"/>
-      <c r="B123" s="12"/>
-    </row>
-    <row r="124" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A124" s="12"/>
-      <c r="B124" s="12"/>
-    </row>
-    <row r="125" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A125" s="12"/>
-      <c r="B125" s="12"/>
-    </row>
-    <row r="126" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A126" s="12"/>
-      <c r="B126" s="12"/>
-    </row>
-    <row r="127" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A127" s="12"/>
-      <c r="B127" s="12"/>
-    </row>
-    <row r="128" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A128" s="12"/>
-      <c r="B128" s="12"/>
-    </row>
-    <row r="129" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A129" s="12"/>
-      <c r="B129" s="12"/>
-    </row>
-    <row r="130" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A130" s="12"/>
-      <c r="B130" s="12"/>
-    </row>
-    <row r="131" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A131" s="12"/>
-      <c r="B131" s="12"/>
-    </row>
-    <row r="132" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A132" s="12"/>
-      <c r="B132" s="12"/>
-    </row>
-    <row r="133" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A133" s="12"/>
-      <c r="B133" s="12"/>
-    </row>
-    <row r="134" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A134" s="12"/>
-      <c r="B134" s="12"/>
-    </row>
-    <row r="135" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A135" s="12"/>
-      <c r="B135" s="12"/>
-    </row>
-    <row r="136" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A136" s="12"/>
-      <c r="B136" s="12"/>
-    </row>
-    <row r="137" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A137" s="12"/>
-      <c r="B137" s="12"/>
-    </row>
-    <row r="138" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A138" s="12"/>
-      <c r="B138" s="12"/>
-    </row>
-    <row r="139" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A139" s="12"/>
-      <c r="B139" s="12"/>
-    </row>
-    <row r="140" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A140" s="12"/>
-      <c r="B140" s="12"/>
-    </row>
-    <row r="141" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A141" s="12"/>
-      <c r="B141" s="12"/>
-    </row>
-    <row r="142" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A142" s="12"/>
-      <c r="B142" s="12"/>
-    </row>
-    <row r="143" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A143" s="12"/>
-      <c r="B143" s="12"/>
-    </row>
-    <row r="144" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A144" s="12"/>
-      <c r="B144" s="12"/>
-    </row>
-    <row r="145" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A145" s="12"/>
-      <c r="B145" s="12"/>
-    </row>
-    <row r="146" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A146" s="12"/>
-      <c r="B146" s="12"/>
-    </row>
-    <row r="147" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A147" s="12"/>
-      <c r="B147" s="12"/>
-    </row>
-    <row r="148" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A148" s="12"/>
-      <c r="B148" s="12"/>
-    </row>
-    <row r="149" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A149" s="12"/>
-      <c r="B149" s="12"/>
-    </row>
-    <row r="150" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A150" s="12"/>
-      <c r="B150" s="12"/>
-    </row>
-    <row r="151" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A151" s="12"/>
-      <c r="B151" s="12"/>
-    </row>
-    <row r="152" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A152" s="12"/>
-      <c r="B152" s="12"/>
-    </row>
-    <row r="153" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A153" s="12"/>
-      <c r="B153" s="12"/>
-    </row>
-    <row r="154" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A154" s="12"/>
-      <c r="B154" s="12"/>
-    </row>
-    <row r="155" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A155" s="12"/>
-      <c r="B155" s="12"/>
-    </row>
-    <row r="156" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A156" s="12"/>
-      <c r="B156" s="12"/>
-    </row>
-    <row r="157" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A157" s="12"/>
-      <c r="B157" s="12"/>
-    </row>
-    <row r="158" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A158" s="12"/>
-      <c r="B158" s="12"/>
-    </row>
-    <row r="159" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A159" s="12"/>
-      <c r="B159" s="12"/>
-    </row>
-    <row r="160" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A160" s="12"/>
-      <c r="B160" s="12"/>
-    </row>
-    <row r="161" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A161" s="12"/>
-      <c r="B161" s="12"/>
-    </row>
-    <row r="162" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A162" s="12"/>
-      <c r="B162" s="12"/>
-    </row>
-    <row r="163" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A163" s="12"/>
-      <c r="B163" s="12"/>
-    </row>
-    <row r="164" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A164" s="12"/>
-      <c r="B164" s="12"/>
-    </row>
-    <row r="165" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A165" s="12"/>
-      <c r="B165" s="12"/>
-    </row>
-    <row r="166" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A166" s="12"/>
-      <c r="B166" s="12"/>
-    </row>
-    <row r="167" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="168" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="169" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="170" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="171" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="172" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="173" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="174" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="175" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="176" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="13"/>
+      <c r="B43" s="13"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="13"/>
+      <c r="B44" s="13"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="13"/>
+      <c r="B45" s="13"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="13"/>
+      <c r="B46" s="13"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="13"/>
+      <c r="B47" s="13"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="13"/>
+      <c r="B48" s="13"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="13"/>
+      <c r="B49" s="13"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="13"/>
+      <c r="B50" s="13"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="13"/>
+      <c r="B51" s="13"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="13"/>
+      <c r="B53" s="13"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="13"/>
+      <c r="B54" s="13"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="13"/>
+      <c r="B55" s="13"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="13"/>
+      <c r="B56" s="13"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="13"/>
+      <c r="B57" s="13"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="13"/>
+      <c r="B58" s="13"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="13"/>
+      <c r="B59" s="13"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="13"/>
+      <c r="B61" s="13"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="13"/>
+      <c r="B62" s="13"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="13"/>
+      <c r="B63" s="13"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="13"/>
+      <c r="B64" s="13"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="13"/>
+      <c r="B65" s="13"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="13"/>
+      <c r="B66" s="13"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="13"/>
+      <c r="B67" s="13"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="13"/>
+      <c r="B68" s="13"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="13"/>
+      <c r="B69" s="13"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="13"/>
+      <c r="B70" s="13"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="13"/>
+      <c r="B71" s="13"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="13"/>
+      <c r="B72" s="13"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="13"/>
+      <c r="B73" s="13"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="13"/>
+      <c r="B74" s="13"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="13"/>
+      <c r="B75" s="13"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="13"/>
+      <c r="B76" s="13"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="13"/>
+      <c r="B77" s="13"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="13"/>
+      <c r="B78" s="13"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="13"/>
+      <c r="B79" s="13"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="13"/>
+      <c r="B80" s="13"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="13"/>
+      <c r="B81" s="13"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="13"/>
+      <c r="B82" s="13"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="13"/>
+      <c r="B83" s="13"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="13"/>
+      <c r="B84" s="13"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="13"/>
+      <c r="B85" s="13"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="13"/>
+      <c r="B86" s="13"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="13"/>
+      <c r="B87" s="13"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="13"/>
+      <c r="B88" s="13"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="13"/>
+      <c r="B89" s="13"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="13"/>
+      <c r="B90" s="13"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="13"/>
+      <c r="B91" s="13"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="13"/>
+      <c r="B92" s="13"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="13"/>
+      <c r="B93" s="13"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="13"/>
+      <c r="B94" s="13"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="13"/>
+      <c r="B95" s="13"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="13"/>
+      <c r="B96" s="13"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="13"/>
+      <c r="B97" s="13"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="13"/>
+      <c r="B98" s="13"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="13"/>
+      <c r="B99" s="13"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="13"/>
+      <c r="B100" s="13"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="13"/>
+      <c r="B101" s="13"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="13"/>
+      <c r="B102" s="13"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="13"/>
+      <c r="B103" s="13"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="13"/>
+      <c r="B104" s="13"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="13"/>
+      <c r="B105" s="13"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="13"/>
+      <c r="B106" s="13"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="13"/>
+      <c r="B107" s="13"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="13"/>
+      <c r="B108" s="13"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="13"/>
+      <c r="B109" s="13"/>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="13"/>
+      <c r="B110" s="13"/>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="13"/>
+      <c r="B111" s="13"/>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="13"/>
+      <c r="B112" s="13"/>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="13"/>
+      <c r="B113" s="13"/>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="13"/>
+      <c r="B114" s="13"/>
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="13"/>
+      <c r="B115" s="13"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="13"/>
+      <c r="B116" s="13"/>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="13"/>
+      <c r="B117" s="13"/>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="13"/>
+      <c r="B118" s="13"/>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="13"/>
+      <c r="B119" s="13"/>
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="13"/>
+      <c r="B120" s="13"/>
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="13"/>
+      <c r="B121" s="13"/>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="13"/>
+      <c r="B122" s="13"/>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="13"/>
+      <c r="B123" s="13"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="13"/>
+      <c r="B124" s="13"/>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="13"/>
+      <c r="B125" s="13"/>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="13"/>
+      <c r="B126" s="13"/>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="13"/>
+      <c r="B127" s="13"/>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="13"/>
+      <c r="B128" s="13"/>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="13"/>
+      <c r="B129" s="13"/>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="13"/>
+      <c r="B130" s="13"/>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="13"/>
+      <c r="B131" s="13"/>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="13"/>
+      <c r="B132" s="13"/>
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="13"/>
+      <c r="B133" s="13"/>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="13"/>
+      <c r="B134" s="13"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="13"/>
+      <c r="B135" s="13"/>
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="13"/>
+      <c r="B136" s="13"/>
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="13"/>
+      <c r="B137" s="13"/>
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="13"/>
+      <c r="B138" s="13"/>
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="13"/>
+      <c r="B139" s="13"/>
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="13"/>
+      <c r="B140" s="13"/>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="13"/>
+      <c r="B141" s="13"/>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="13"/>
+      <c r="B142" s="13"/>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="13"/>
+      <c r="B143" s="13"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="13"/>
+      <c r="B144" s="13"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="13"/>
+      <c r="B145" s="13"/>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="13"/>
+      <c r="B146" s="13"/>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="13"/>
+      <c r="B147" s="13"/>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="13"/>
+      <c r="B148" s="13"/>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="13"/>
+      <c r="B149" s="13"/>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="13"/>
+      <c r="B150" s="13"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="13"/>
+      <c r="B151" s="13"/>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="13"/>
+      <c r="B152" s="13"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="13"/>
+      <c r="B153" s="13"/>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="13"/>
+      <c r="B154" s="13"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="13"/>
+      <c r="B155" s="13"/>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="13"/>
+      <c r="B156" s="13"/>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="13"/>
+      <c r="B157" s="13"/>
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="13"/>
+      <c r="B158" s="13"/>
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="13"/>
+      <c r="B159" s="13"/>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="13"/>
+      <c r="B160" s="13"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="13"/>
+      <c r="B161" s="13"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="13"/>
+      <c r="B162" s="13"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="13"/>
+      <c r="B163" s="13"/>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="13"/>
+      <c r="B164" s="13"/>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="13"/>
+      <c r="B165" s="13"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="13"/>
+      <c r="B166" s="13"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
     <row r="177" ht="15.75" customHeight="1"/>
     <row r="178" ht="15.75" customHeight="1"/>
     <row r="179" ht="15.75" customHeight="1"/>
@@ -2263,14 +2233,10 @@
     <row r="943" ht="15.75" customHeight="1"/>
     <row r="944" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="J1:O12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <autoFilter ref="$J$1:$O$12"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{08f6f869-1ed0-46b3-a227-1d3e52347e28}" enabled="1" method="Standard" siteId="{98e9ba89-e1a1-4e38-9007-8bdabc25de1d}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="24">
   <si>
     <t>Game</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>Hugo</t>
-  </si>
-  <si>
-    <t>Micah</t>
   </si>
   <si>
     <t>Mulu</t>
@@ -506,7 +503,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="4">
-        <f t="shared" ref="O2:O11" si="3">K2*2+SUM(L2:N2)</f>
+        <f t="shared" ref="O2:O10" si="3">K2*2+SUM(L2:N2)</f>
         <v>2</v>
       </c>
     </row>
@@ -793,7 +790,7 @@
       </c>
       <c r="M8" s="4">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="4">
         <f t="shared" si="8"/>
@@ -801,7 +798,7 @@
       </c>
       <c r="O8" s="4">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -830,7 +827,7 @@
         <v>13</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K9" s="4">
         <f t="shared" ref="K9:N9" si="9">COUNTIF(E$2:E$964,$J9)</f>
@@ -838,19 +835,19 @@
       </c>
       <c r="L9" s="4">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="4">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="4">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -873,21 +870,21 @@
         <v>21</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K10" s="4">
         <f t="shared" ref="K10:N10" si="10">COUNTIF(E$2:E$964,$J10)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="4">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="4">
         <f t="shared" si="10"/>
@@ -899,34 +896,10 @@
       </c>
       <c r="O10" s="4">
         <f t="shared" si="3"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="J11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K11" s="4">
-        <f t="shared" ref="K11:N11" si="11">COUNTIF(E$2:E$964,$J11)</f>
-        <v>1</v>
-      </c>
-      <c r="L11" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <f t="shared" si="11"/>
-        <v>1</v>
-      </c>
-      <c r="O11" s="4">
-        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
+    <row r="11" ht="15.75" customHeight="1"/>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1"/>

--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -11,14 +11,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="C6zCwR/TZey+cf8qVItD04OlODhU8xubcFG/MqVZmog="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="hAP4UIhaZFTWDrlyntcriY5kOLup6gTT+4V7mbtJkOg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="24">
   <si>
     <t>Game</t>
   </si>
@@ -99,7 +99,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -126,6 +126,11 @@
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -168,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -191,6 +196,14 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -487,12 +500,12 @@
         <v>14</v>
       </c>
       <c r="K2" s="4">
-        <f t="shared" ref="K2:N2" si="1">COUNTIF(E$2:E$964,$J2)</f>
+        <f t="shared" ref="K2:N2" si="1">COUNTIF(E$2:E$963,$J2)</f>
         <v>0</v>
       </c>
       <c r="L2" s="4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" s="4">
         <f t="shared" si="1"/>
@@ -504,7 +517,7 @@
       </c>
       <c r="O2" s="4">
         <f t="shared" ref="O2:O10" si="3">K2*2+SUM(L2:N2)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -536,7 +549,7 @@
         <v>15</v>
       </c>
       <c r="K3" s="4">
-        <f t="shared" ref="K3:N3" si="2">COUNTIF(E$2:E$964,$J3)</f>
+        <f t="shared" ref="K3:N3" si="2">COUNTIF(E$2:E$963,$J3)</f>
         <v>1</v>
       </c>
       <c r="L3" s="4">
@@ -549,11 +562,11 @@
       </c>
       <c r="N3" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O3" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -585,8 +598,8 @@
         <v>16</v>
       </c>
       <c r="K4" s="4">
-        <f t="shared" ref="K4:N4" si="4">COUNTIF(E$2:E$964,$J4)</f>
-        <v>1</v>
+        <f t="shared" ref="K4:N4" si="4">COUNTIF(E$2:E$963,$J4)</f>
+        <v>2</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="4"/>
@@ -602,7 +615,7 @@
       </c>
       <c r="O4" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -634,7 +647,7 @@
         <v>19</v>
       </c>
       <c r="K5" s="4">
-        <f t="shared" ref="K5:N5" si="5">COUNTIF(E$2:E$964,$J5)</f>
+        <f t="shared" ref="K5:N5" si="5">COUNTIF(E$2:E$963,$J5)</f>
         <v>1</v>
       </c>
       <c r="L5" s="4">
@@ -647,11 +660,11 @@
       </c>
       <c r="N5" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -683,12 +696,12 @@
         <v>22</v>
       </c>
       <c r="K6" s="4">
-        <f t="shared" ref="K6:N6" si="6">COUNTIF(E$2:E$964,$J6)</f>
+        <f t="shared" ref="K6:N6" si="6">COUNTIF(E$2:E$963,$J6)</f>
         <v>1</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="6"/>
@@ -696,11 +709,11 @@
       </c>
       <c r="N6" s="4">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="4">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -732,7 +745,7 @@
         <v>18</v>
       </c>
       <c r="K7" s="4">
-        <f t="shared" ref="K7:N7" si="7">COUNTIF(E$2:E$964,$J7)</f>
+        <f t="shared" ref="K7:N7" si="7">COUNTIF(E$2:E$963,$J7)</f>
         <v>1</v>
       </c>
       <c r="L7" s="4">
@@ -781,7 +794,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="4">
-        <f t="shared" ref="K8:N8" si="8">COUNTIF(E$2:E$964,$J8)</f>
+        <f t="shared" ref="K8:N8" si="8">COUNTIF(E$2:E$963,$J8)</f>
         <v>0</v>
       </c>
       <c r="L8" s="4">
@@ -790,7 +803,7 @@
       </c>
       <c r="M8" s="4">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N8" s="4">
         <f t="shared" si="8"/>
@@ -798,7 +811,7 @@
       </c>
       <c r="O8" s="4">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -830,8 +843,8 @@
         <v>21</v>
       </c>
       <c r="K9" s="4">
-        <f t="shared" ref="K9:N9" si="9">COUNTIF(E$2:E$964,$J9)</f>
-        <v>0</v>
+        <f t="shared" ref="K9:N9" si="9">COUNTIF(E$2:E$963,$J9)</f>
+        <v>1</v>
       </c>
       <c r="L9" s="4">
         <f t="shared" si="9"/>
@@ -839,7 +852,7 @@
       </c>
       <c r="M9" s="4">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="4">
         <f t="shared" si="9"/>
@@ -847,7 +860,7 @@
       </c>
       <c r="O9" s="4">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -879,8 +892,8 @@
         <v>12</v>
       </c>
       <c r="K10" s="4">
-        <f t="shared" ref="K10:N10" si="10">COUNTIF(E$2:E$964,$J10)</f>
-        <v>1</v>
+        <f t="shared" ref="K10:N10" si="10">COUNTIF(E$2:E$963,$J10)</f>
+        <v>2</v>
       </c>
       <c r="L10" s="4">
         <f t="shared" si="10"/>
@@ -896,16 +909,161 @@
       </c>
       <c r="O10" s="4">
         <f t="shared" si="3"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1"/>
-    <row r="12" ht="15.75" customHeight="1"/>
-    <row r="13" ht="15.75" customHeight="1"/>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46319.0</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="B12" s="6">
+        <v>46326.0</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="5">
+        <v>11.0</v>
+      </c>
+      <c r="B13" s="6">
+        <v>46333.0</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="B14" s="6">
+        <v>46340.0</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="5">
+        <v>13.0</v>
+      </c>
+      <c r="B15" s="6">
+        <v>46347.0</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="5">
+        <v>14.0</v>
+      </c>
+      <c r="B16" s="16">
+        <v>46354.0</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="5">
+        <v>15.0</v>
+      </c>
+      <c r="B17" s="6">
+        <v>46361.0</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -930,503 +1088,503 @@
     <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+    </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="13"/>
-      <c r="B46" s="13"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="13"/>
-      <c r="B47" s="13"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="13"/>
-      <c r="B49" s="13"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="13"/>
-      <c r="B50" s="13"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="13"/>
-      <c r="B53" s="13"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="13"/>
-      <c r="B54" s="13"/>
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="13"/>
-      <c r="B55" s="13"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="13"/>
-      <c r="B58" s="13"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="13"/>
-      <c r="B60" s="13"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="13"/>
-      <c r="B61" s="13"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="13"/>
-      <c r="B62" s="13"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="17"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="13"/>
-      <c r="B63" s="13"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="17"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="13"/>
-      <c r="B64" s="13"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="13"/>
-      <c r="B65" s="13"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="13"/>
-      <c r="B66" s="13"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="13"/>
-      <c r="B67" s="13"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="13"/>
-      <c r="B68" s="13"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="13"/>
-      <c r="B69" s="13"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="17"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="13"/>
-      <c r="B70" s="13"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="17"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="13"/>
-      <c r="B71" s="13"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="13"/>
-      <c r="B72" s="13"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="13"/>
-      <c r="B73" s="13"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="17"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="13"/>
-      <c r="B74" s="13"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="17"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="13"/>
-      <c r="B75" s="13"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="17"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="13"/>
-      <c r="B76" s="13"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="17"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="13"/>
-      <c r="B77" s="13"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="17"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="13"/>
-      <c r="B78" s="13"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="17"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="13"/>
-      <c r="B79" s="13"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="17"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="13"/>
-      <c r="B80" s="13"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="17"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="13"/>
-      <c r="B81" s="13"/>
+      <c r="A81" s="17"/>
+      <c r="B81" s="17"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="13"/>
-      <c r="B82" s="13"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="17"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="13"/>
-      <c r="B83" s="13"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="17"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="13"/>
-      <c r="B84" s="13"/>
+      <c r="A84" s="17"/>
+      <c r="B84" s="17"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="13"/>
-      <c r="B85" s="13"/>
+      <c r="A85" s="17"/>
+      <c r="B85" s="17"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="13"/>
-      <c r="B86" s="13"/>
+      <c r="A86" s="17"/>
+      <c r="B86" s="17"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="13"/>
-      <c r="B87" s="13"/>
+      <c r="A87" s="17"/>
+      <c r="B87" s="17"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="13"/>
-      <c r="B88" s="13"/>
+      <c r="A88" s="17"/>
+      <c r="B88" s="17"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="13"/>
-      <c r="B89" s="13"/>
+      <c r="A89" s="17"/>
+      <c r="B89" s="17"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="13"/>
-      <c r="B90" s="13"/>
+      <c r="A90" s="17"/>
+      <c r="B90" s="17"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="13"/>
-      <c r="B91" s="13"/>
+      <c r="A91" s="17"/>
+      <c r="B91" s="17"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="13"/>
-      <c r="B92" s="13"/>
+      <c r="A92" s="17"/>
+      <c r="B92" s="17"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="13"/>
-      <c r="B93" s="13"/>
+      <c r="A93" s="17"/>
+      <c r="B93" s="17"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="13"/>
-      <c r="B94" s="13"/>
+      <c r="A94" s="17"/>
+      <c r="B94" s="17"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="13"/>
-      <c r="B95" s="13"/>
+      <c r="A95" s="17"/>
+      <c r="B95" s="17"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="13"/>
-      <c r="B96" s="13"/>
+      <c r="A96" s="17"/>
+      <c r="B96" s="17"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="13"/>
-      <c r="B97" s="13"/>
+      <c r="A97" s="17"/>
+      <c r="B97" s="17"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="13"/>
-      <c r="B98" s="13"/>
+      <c r="A98" s="17"/>
+      <c r="B98" s="17"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="13"/>
-      <c r="B99" s="13"/>
+      <c r="A99" s="17"/>
+      <c r="B99" s="17"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="13"/>
-      <c r="B100" s="13"/>
+      <c r="A100" s="17"/>
+      <c r="B100" s="17"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="13"/>
-      <c r="B101" s="13"/>
+      <c r="A101" s="17"/>
+      <c r="B101" s="17"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="13"/>
-      <c r="B102" s="13"/>
+      <c r="A102" s="17"/>
+      <c r="B102" s="17"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="13"/>
-      <c r="B103" s="13"/>
+      <c r="A103" s="17"/>
+      <c r="B103" s="17"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="13"/>
-      <c r="B104" s="13"/>
+      <c r="A104" s="17"/>
+      <c r="B104" s="17"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="13"/>
-      <c r="B105" s="13"/>
+      <c r="A105" s="17"/>
+      <c r="B105" s="17"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="13"/>
-      <c r="B106" s="13"/>
+      <c r="A106" s="17"/>
+      <c r="B106" s="17"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="13"/>
-      <c r="B107" s="13"/>
+      <c r="A107" s="17"/>
+      <c r="B107" s="17"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="13"/>
-      <c r="B108" s="13"/>
+      <c r="A108" s="17"/>
+      <c r="B108" s="17"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="13"/>
-      <c r="B109" s="13"/>
+      <c r="A109" s="17"/>
+      <c r="B109" s="17"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="13"/>
-      <c r="B110" s="13"/>
+      <c r="A110" s="17"/>
+      <c r="B110" s="17"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="13"/>
-      <c r="B111" s="13"/>
+      <c r="A111" s="17"/>
+      <c r="B111" s="17"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="13"/>
-      <c r="B112" s="13"/>
+      <c r="A112" s="17"/>
+      <c r="B112" s="17"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="13"/>
-      <c r="B113" s="13"/>
+      <c r="A113" s="17"/>
+      <c r="B113" s="17"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="13"/>
-      <c r="B114" s="13"/>
+      <c r="A114" s="17"/>
+      <c r="B114" s="17"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="13"/>
-      <c r="B115" s="13"/>
+      <c r="A115" s="17"/>
+      <c r="B115" s="17"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="13"/>
-      <c r="B116" s="13"/>
+      <c r="A116" s="17"/>
+      <c r="B116" s="17"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="13"/>
-      <c r="B117" s="13"/>
+      <c r="A117" s="17"/>
+      <c r="B117" s="17"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="13"/>
-      <c r="B118" s="13"/>
+      <c r="A118" s="17"/>
+      <c r="B118" s="17"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="13"/>
-      <c r="B119" s="13"/>
+      <c r="A119" s="17"/>
+      <c r="B119" s="17"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="13"/>
-      <c r="B120" s="13"/>
+      <c r="A120" s="17"/>
+      <c r="B120" s="17"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="13"/>
-      <c r="B121" s="13"/>
+      <c r="A121" s="17"/>
+      <c r="B121" s="17"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="13"/>
-      <c r="B122" s="13"/>
+      <c r="A122" s="17"/>
+      <c r="B122" s="17"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="13"/>
-      <c r="B123" s="13"/>
+      <c r="A123" s="17"/>
+      <c r="B123" s="17"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="13"/>
-      <c r="B124" s="13"/>
+      <c r="A124" s="17"/>
+      <c r="B124" s="17"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="13"/>
-      <c r="B125" s="13"/>
+      <c r="A125" s="17"/>
+      <c r="B125" s="17"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="13"/>
-      <c r="B126" s="13"/>
+      <c r="A126" s="17"/>
+      <c r="B126" s="17"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="13"/>
-      <c r="B127" s="13"/>
+      <c r="A127" s="17"/>
+      <c r="B127" s="17"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="13"/>
-      <c r="B128" s="13"/>
+      <c r="A128" s="17"/>
+      <c r="B128" s="17"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="13"/>
-      <c r="B129" s="13"/>
+      <c r="A129" s="17"/>
+      <c r="B129" s="17"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="13"/>
-      <c r="B130" s="13"/>
+      <c r="A130" s="17"/>
+      <c r="B130" s="17"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="13"/>
-      <c r="B131" s="13"/>
+      <c r="A131" s="17"/>
+      <c r="B131" s="17"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="13"/>
-      <c r="B132" s="13"/>
+      <c r="A132" s="17"/>
+      <c r="B132" s="17"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="13"/>
-      <c r="B133" s="13"/>
+      <c r="A133" s="17"/>
+      <c r="B133" s="17"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="13"/>
-      <c r="B134" s="13"/>
+      <c r="A134" s="17"/>
+      <c r="B134" s="17"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="13"/>
-      <c r="B135" s="13"/>
+      <c r="A135" s="17"/>
+      <c r="B135" s="17"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="13"/>
-      <c r="B136" s="13"/>
+      <c r="A136" s="17"/>
+      <c r="B136" s="17"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="13"/>
-      <c r="B137" s="13"/>
+      <c r="A137" s="17"/>
+      <c r="B137" s="17"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="13"/>
-      <c r="B138" s="13"/>
+      <c r="A138" s="17"/>
+      <c r="B138" s="17"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="13"/>
-      <c r="B139" s="13"/>
+      <c r="A139" s="17"/>
+      <c r="B139" s="17"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="13"/>
-      <c r="B140" s="13"/>
+      <c r="A140" s="17"/>
+      <c r="B140" s="17"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="13"/>
-      <c r="B141" s="13"/>
+      <c r="A141" s="17"/>
+      <c r="B141" s="17"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="13"/>
-      <c r="B142" s="13"/>
+      <c r="A142" s="17"/>
+      <c r="B142" s="17"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="13"/>
-      <c r="B143" s="13"/>
+      <c r="A143" s="17"/>
+      <c r="B143" s="17"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="13"/>
-      <c r="B144" s="13"/>
+      <c r="A144" s="17"/>
+      <c r="B144" s="17"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="13"/>
-      <c r="B145" s="13"/>
+      <c r="A145" s="17"/>
+      <c r="B145" s="17"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="13"/>
-      <c r="B146" s="13"/>
+      <c r="A146" s="17"/>
+      <c r="B146" s="17"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="13"/>
-      <c r="B147" s="13"/>
+      <c r="A147" s="17"/>
+      <c r="B147" s="17"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="13"/>
-      <c r="B148" s="13"/>
+      <c r="A148" s="17"/>
+      <c r="B148" s="17"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="13"/>
-      <c r="B149" s="13"/>
+      <c r="A149" s="17"/>
+      <c r="B149" s="17"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="13"/>
-      <c r="B150" s="13"/>
+      <c r="A150" s="17"/>
+      <c r="B150" s="17"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="13"/>
-      <c r="B151" s="13"/>
+      <c r="A151" s="17"/>
+      <c r="B151" s="17"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="13"/>
-      <c r="B152" s="13"/>
+      <c r="A152" s="17"/>
+      <c r="B152" s="17"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="13"/>
-      <c r="B153" s="13"/>
+      <c r="A153" s="17"/>
+      <c r="B153" s="17"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="13"/>
-      <c r="B154" s="13"/>
+      <c r="A154" s="17"/>
+      <c r="B154" s="17"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="13"/>
-      <c r="B155" s="13"/>
+      <c r="A155" s="17"/>
+      <c r="B155" s="17"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="13"/>
-      <c r="B156" s="13"/>
+      <c r="A156" s="17"/>
+      <c r="B156" s="17"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="13"/>
-      <c r="B157" s="13"/>
+      <c r="A157" s="17"/>
+      <c r="B157" s="17"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="13"/>
-      <c r="B158" s="13"/>
+      <c r="A158" s="17"/>
+      <c r="B158" s="17"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="13"/>
-      <c r="B159" s="13"/>
+      <c r="A159" s="17"/>
+      <c r="B159" s="17"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="13"/>
-      <c r="B160" s="13"/>
+      <c r="A160" s="17"/>
+      <c r="B160" s="17"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="13"/>
-      <c r="B161" s="13"/>
+      <c r="A161" s="17"/>
+      <c r="B161" s="17"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="13"/>
-      <c r="B162" s="13"/>
+      <c r="A162" s="17"/>
+      <c r="B162" s="17"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="13"/>
-      <c r="B163" s="13"/>
+      <c r="A163" s="17"/>
+      <c r="B163" s="17"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="13"/>
-      <c r="B164" s="13"/>
+      <c r="A164" s="17"/>
+      <c r="B164" s="17"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="13"/>
-      <c r="B165" s="13"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="13"/>
-      <c r="B166" s="13"/>
-    </row>
+      <c r="A165" s="17"/>
+      <c r="B165" s="17"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1"/>
     <row r="167" ht="15.75" customHeight="1"/>
     <row r="168" ht="15.75" customHeight="1"/>
     <row r="169" ht="15.75" customHeight="1"/>
@@ -2204,7 +2362,6 @@
     <row r="941" ht="15.75" customHeight="1"/>
     <row r="942" ht="15.75" customHeight="1"/>
     <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="$J$1:$O$12"/>
   <printOptions/>

--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -173,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -202,6 +202,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
@@ -424,7 +427,7 @@
   <cols>
     <col customWidth="1" min="1" max="8" width="17.0"/>
     <col customWidth="1" min="9" max="9" width="12.38"/>
-    <col customWidth="1" min="10" max="10" width="15.63"/>
+    <col customWidth="1" min="10" max="15" width="9.25"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -754,7 +757,7 @@
       </c>
       <c r="M7" s="4">
         <f t="shared" si="7"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" s="4">
         <f t="shared" si="7"/>
@@ -762,7 +765,7 @@
       </c>
       <c r="O7" s="4">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -852,7 +855,7 @@
       </c>
       <c r="M9" s="4">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" s="4">
         <f t="shared" si="9"/>
@@ -860,7 +863,7 @@
       </c>
       <c r="O9" s="4">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -928,8 +931,8 @@
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
       <c r="G11" s="14"/>
-      <c r="H11" s="13" t="s">
-        <v>22</v>
+      <c r="H11" s="15" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -996,7 +999,7 @@
         <v>22</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H14" s="14"/>
     </row>
@@ -1016,15 +1019,15 @@
       <c r="E15" s="14"/>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
-      <c r="H15" s="15" t="s">
-        <v>15</v>
+      <c r="H15" s="16" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="5">
         <v>14.0</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="17">
         <v>46354.0</v>
       </c>
       <c r="C16" s="13" t="s">
@@ -1089,500 +1092,500 @@
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="17"/>
-      <c r="B57" s="17"/>
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="17"/>
-      <c r="B58" s="17"/>
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="17"/>
-      <c r="B59" s="17"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="17"/>
-      <c r="B60" s="17"/>
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="17"/>
-      <c r="B61" s="17"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="17"/>
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="17"/>
-      <c r="B67" s="17"/>
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="17"/>
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="17"/>
-      <c r="B69" s="17"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="17"/>
-      <c r="B70" s="17"/>
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="17"/>
-      <c r="B71" s="17"/>
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="17"/>
-      <c r="B72" s="17"/>
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="17"/>
-      <c r="B73" s="17"/>
+      <c r="A73" s="18"/>
+      <c r="B73" s="18"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="17"/>
-      <c r="B74" s="17"/>
+      <c r="A74" s="18"/>
+      <c r="B74" s="18"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="17"/>
-      <c r="B75" s="17"/>
+      <c r="A75" s="18"/>
+      <c r="B75" s="18"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="17"/>
-      <c r="B76" s="17"/>
+      <c r="A76" s="18"/>
+      <c r="B76" s="18"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="17"/>
-      <c r="B77" s="17"/>
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="17"/>
-      <c r="B78" s="17"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="17"/>
-      <c r="B79" s="17"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="17"/>
-      <c r="B80" s="17"/>
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="17"/>
-      <c r="B81" s="17"/>
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="17"/>
-      <c r="B82" s="17"/>
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="17"/>
-      <c r="B83" s="17"/>
+      <c r="A83" s="18"/>
+      <c r="B83" s="18"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="17"/>
-      <c r="B84" s="17"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="17"/>
-      <c r="B85" s="17"/>
+      <c r="A85" s="18"/>
+      <c r="B85" s="18"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="17"/>
-      <c r="B86" s="17"/>
+      <c r="A86" s="18"/>
+      <c r="B86" s="18"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="17"/>
-      <c r="B87" s="17"/>
+      <c r="A87" s="18"/>
+      <c r="B87" s="18"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="17"/>
-      <c r="B88" s="17"/>
+      <c r="A88" s="18"/>
+      <c r="B88" s="18"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="17"/>
-      <c r="B89" s="17"/>
+      <c r="A89" s="18"/>
+      <c r="B89" s="18"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="17"/>
-      <c r="B90" s="17"/>
+      <c r="A90" s="18"/>
+      <c r="B90" s="18"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="17"/>
-      <c r="B91" s="17"/>
+      <c r="A91" s="18"/>
+      <c r="B91" s="18"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="17"/>
-      <c r="B92" s="17"/>
+      <c r="A92" s="18"/>
+      <c r="B92" s="18"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="17"/>
-      <c r="B93" s="17"/>
+      <c r="A93" s="18"/>
+      <c r="B93" s="18"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="17"/>
-      <c r="B94" s="17"/>
+      <c r="A94" s="18"/>
+      <c r="B94" s="18"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="17"/>
-      <c r="B95" s="17"/>
+      <c r="A95" s="18"/>
+      <c r="B95" s="18"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="17"/>
-      <c r="B96" s="17"/>
+      <c r="A96" s="18"/>
+      <c r="B96" s="18"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="17"/>
-      <c r="B97" s="17"/>
+      <c r="A97" s="18"/>
+      <c r="B97" s="18"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="17"/>
-      <c r="B98" s="17"/>
+      <c r="A98" s="18"/>
+      <c r="B98" s="18"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="17"/>
-      <c r="B99" s="17"/>
+      <c r="A99" s="18"/>
+      <c r="B99" s="18"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="17"/>
-      <c r="B100" s="17"/>
+      <c r="A100" s="18"/>
+      <c r="B100" s="18"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="17"/>
-      <c r="B101" s="17"/>
+      <c r="A101" s="18"/>
+      <c r="B101" s="18"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="17"/>
-      <c r="B102" s="17"/>
+      <c r="A102" s="18"/>
+      <c r="B102" s="18"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="17"/>
-      <c r="B103" s="17"/>
+      <c r="A103" s="18"/>
+      <c r="B103" s="18"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="17"/>
-      <c r="B104" s="17"/>
+      <c r="A104" s="18"/>
+      <c r="B104" s="18"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="17"/>
-      <c r="B105" s="17"/>
+      <c r="A105" s="18"/>
+      <c r="B105" s="18"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="17"/>
-      <c r="B106" s="17"/>
+      <c r="A106" s="18"/>
+      <c r="B106" s="18"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="17"/>
-      <c r="B107" s="17"/>
+      <c r="A107" s="18"/>
+      <c r="B107" s="18"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="17"/>
-      <c r="B108" s="17"/>
+      <c r="A108" s="18"/>
+      <c r="B108" s="18"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="17"/>
-      <c r="B109" s="17"/>
+      <c r="A109" s="18"/>
+      <c r="B109" s="18"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="17"/>
-      <c r="B110" s="17"/>
+      <c r="A110" s="18"/>
+      <c r="B110" s="18"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="17"/>
-      <c r="B111" s="17"/>
+      <c r="A111" s="18"/>
+      <c r="B111" s="18"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="17"/>
-      <c r="B112" s="17"/>
+      <c r="A112" s="18"/>
+      <c r="B112" s="18"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="17"/>
-      <c r="B113" s="17"/>
+      <c r="A113" s="18"/>
+      <c r="B113" s="18"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="17"/>
-      <c r="B114" s="17"/>
+      <c r="A114" s="18"/>
+      <c r="B114" s="18"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="17"/>
-      <c r="B115" s="17"/>
+      <c r="A115" s="18"/>
+      <c r="B115" s="18"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="17"/>
-      <c r="B116" s="17"/>
+      <c r="A116" s="18"/>
+      <c r="B116" s="18"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="17"/>
-      <c r="B117" s="17"/>
+      <c r="A117" s="18"/>
+      <c r="B117" s="18"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="17"/>
-      <c r="B118" s="17"/>
+      <c r="A118" s="18"/>
+      <c r="B118" s="18"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="17"/>
-      <c r="B119" s="17"/>
+      <c r="A119" s="18"/>
+      <c r="B119" s="18"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="17"/>
-      <c r="B120" s="17"/>
+      <c r="A120" s="18"/>
+      <c r="B120" s="18"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="17"/>
-      <c r="B121" s="17"/>
+      <c r="A121" s="18"/>
+      <c r="B121" s="18"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="17"/>
-      <c r="B122" s="17"/>
+      <c r="A122" s="18"/>
+      <c r="B122" s="18"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="17"/>
-      <c r="B123" s="17"/>
+      <c r="A123" s="18"/>
+      <c r="B123" s="18"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="17"/>
-      <c r="B124" s="17"/>
+      <c r="A124" s="18"/>
+      <c r="B124" s="18"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="17"/>
-      <c r="B125" s="17"/>
+      <c r="A125" s="18"/>
+      <c r="B125" s="18"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="17"/>
-      <c r="B126" s="17"/>
+      <c r="A126" s="18"/>
+      <c r="B126" s="18"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="17"/>
-      <c r="B127" s="17"/>
+      <c r="A127" s="18"/>
+      <c r="B127" s="18"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="17"/>
-      <c r="B128" s="17"/>
+      <c r="A128" s="18"/>
+      <c r="B128" s="18"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="17"/>
-      <c r="B129" s="17"/>
+      <c r="A129" s="18"/>
+      <c r="B129" s="18"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="17"/>
-      <c r="B130" s="17"/>
+      <c r="A130" s="18"/>
+      <c r="B130" s="18"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="17"/>
-      <c r="B131" s="17"/>
+      <c r="A131" s="18"/>
+      <c r="B131" s="18"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="17"/>
-      <c r="B132" s="17"/>
+      <c r="A132" s="18"/>
+      <c r="B132" s="18"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="17"/>
-      <c r="B133" s="17"/>
+      <c r="A133" s="18"/>
+      <c r="B133" s="18"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="17"/>
-      <c r="B134" s="17"/>
+      <c r="A134" s="18"/>
+      <c r="B134" s="18"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="17"/>
-      <c r="B135" s="17"/>
+      <c r="A135" s="18"/>
+      <c r="B135" s="18"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="17"/>
-      <c r="B136" s="17"/>
+      <c r="A136" s="18"/>
+      <c r="B136" s="18"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="17"/>
-      <c r="B137" s="17"/>
+      <c r="A137" s="18"/>
+      <c r="B137" s="18"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="17"/>
-      <c r="B138" s="17"/>
+      <c r="A138" s="18"/>
+      <c r="B138" s="18"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="17"/>
-      <c r="B139" s="17"/>
+      <c r="A139" s="18"/>
+      <c r="B139" s="18"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="17"/>
-      <c r="B140" s="17"/>
+      <c r="A140" s="18"/>
+      <c r="B140" s="18"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="17"/>
-      <c r="B141" s="17"/>
+      <c r="A141" s="18"/>
+      <c r="B141" s="18"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="17"/>
-      <c r="B142" s="17"/>
+      <c r="A142" s="18"/>
+      <c r="B142" s="18"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="17"/>
-      <c r="B143" s="17"/>
+      <c r="A143" s="18"/>
+      <c r="B143" s="18"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="17"/>
-      <c r="B144" s="17"/>
+      <c r="A144" s="18"/>
+      <c r="B144" s="18"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="17"/>
-      <c r="B145" s="17"/>
+      <c r="A145" s="18"/>
+      <c r="B145" s="18"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="17"/>
-      <c r="B146" s="17"/>
+      <c r="A146" s="18"/>
+      <c r="B146" s="18"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="17"/>
-      <c r="B147" s="17"/>
+      <c r="A147" s="18"/>
+      <c r="B147" s="18"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="17"/>
-      <c r="B148" s="17"/>
+      <c r="A148" s="18"/>
+      <c r="B148" s="18"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="17"/>
-      <c r="B149" s="17"/>
+      <c r="A149" s="18"/>
+      <c r="B149" s="18"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="17"/>
-      <c r="B150" s="17"/>
+      <c r="A150" s="18"/>
+      <c r="B150" s="18"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="17"/>
-      <c r="B151" s="17"/>
+      <c r="A151" s="18"/>
+      <c r="B151" s="18"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="17"/>
-      <c r="B152" s="17"/>
+      <c r="A152" s="18"/>
+      <c r="B152" s="18"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="17"/>
-      <c r="B153" s="17"/>
+      <c r="A153" s="18"/>
+      <c r="B153" s="18"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="17"/>
-      <c r="B154" s="17"/>
+      <c r="A154" s="18"/>
+      <c r="B154" s="18"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="17"/>
-      <c r="B155" s="17"/>
+      <c r="A155" s="18"/>
+      <c r="B155" s="18"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="17"/>
-      <c r="B156" s="17"/>
+      <c r="A156" s="18"/>
+      <c r="B156" s="18"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="17"/>
-      <c r="B157" s="17"/>
+      <c r="A157" s="18"/>
+      <c r="B157" s="18"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="17"/>
-      <c r="B158" s="17"/>
+      <c r="A158" s="18"/>
+      <c r="B158" s="18"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="17"/>
-      <c r="B159" s="17"/>
+      <c r="A159" s="18"/>
+      <c r="B159" s="18"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="17"/>
-      <c r="B160" s="17"/>
+      <c r="A160" s="18"/>
+      <c r="B160" s="18"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="17"/>
-      <c r="B161" s="17"/>
+      <c r="A161" s="18"/>
+      <c r="B161" s="18"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="17"/>
-      <c r="B162" s="17"/>
+      <c r="A162" s="18"/>
+      <c r="B162" s="18"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="17"/>
-      <c r="B163" s="17"/>
+      <c r="A163" s="18"/>
+      <c r="B163" s="18"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="17"/>
-      <c r="B164" s="17"/>
+      <c r="A164" s="18"/>
+      <c r="B164" s="18"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="17"/>
-      <c r="B165" s="17"/>
+      <c r="A165" s="18"/>
+      <c r="B165" s="18"/>
     </row>
     <row r="166" ht="15.75" customHeight="1"/>
     <row r="167" ht="15.75" customHeight="1"/>

--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -700,7 +700,7 @@
       </c>
       <c r="K6" s="4">
         <f t="shared" ref="K6:N6" si="6">COUNTIF(E$2:E$963,$J6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="6"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="O6" s="4">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -847,7 +847,7 @@
       </c>
       <c r="K9" s="4">
         <f t="shared" ref="K9:N9" si="9">COUNTIF(E$2:E$963,$J9)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="4">
         <f t="shared" si="9"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="O9" s="4">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -949,7 +949,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F12" s="13" t="s">
         <v>14</v>

--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -602,11 +602,11 @@
       </c>
       <c r="K4" s="4">
         <f t="shared" ref="K4:N4" si="4">COUNTIF(E$2:E$963,$J4)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="4">
         <f t="shared" si="4"/>
@@ -618,7 +618,7 @@
       </c>
       <c r="O4" s="4">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -704,7 +704,7 @@
       </c>
       <c r="L6" s="4">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" si="6"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="O6" s="4">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -847,7 +847,7 @@
       </c>
       <c r="K9" s="4">
         <f t="shared" ref="K9:N9" si="9">COUNTIF(E$2:E$963,$J9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="4">
         <f t="shared" si="9"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="O9" s="4">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -993,10 +993,10 @@
         <v>11</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>18</v>
@@ -1036,8 +1036,8 @@
       <c r="D16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="8" t="s">
-        <v>16</v>
+      <c r="E16" s="12" t="s">
+        <v>12</v>
       </c>
       <c r="F16" s="13" t="s">
         <v>14</v>
